--- a/Modules/X2/X2_BOM.xlsx
+++ b/Modules/X2/X2_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\X2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F575DA-B950-46B7-AFD1-A2ED1A654812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16E107A-05F7-44AA-AE12-688FF2697624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -89,15 +89,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jack Nut</t>
   </si>
   <si>
@@ -108,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
   </si>
   <si>
     <t>R-0603</t>
@@ -253,6 +244,15 @@
   </si>
   <si>
     <t>Avalon Harmonics X2</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1156,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1191,19 +1191,19 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1214,19 +1214,19 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1237,19 +1237,19 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1257,22 +1257,22 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1280,22 +1280,22 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1303,13 +1303,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1329,7 +1329,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1338,10 +1338,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1355,13 +1355,13 @@
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1369,24 +1369,24 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1422,14 +1422,14 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{A893ABC8-5223-47F2-8335-C8AD6F9E7D68}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{B40A6525-E24B-4FF5-BC67-1B758AD6314F}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{B273C29C-FAF1-4C69-8A57-557C938F7138}"/>
-    <hyperlink ref="F3" r:id="rId7" xr:uid="{B1B7F1AE-C00F-4CC2-82E3-32FC3FFE3560}"/>
-    <hyperlink ref="F4" r:id="rId8" xr:uid="{FE6BDE23-52FC-41D4-8B40-F390A9871ADD}"/>
-    <hyperlink ref="F7" r:id="rId9" xr:uid="{4D4556AA-6336-4B9A-B471-3B29E101749D}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{B40A6525-E24B-4FF5-BC67-1B758AD6314F}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{B273C29C-FAF1-4C69-8A57-557C938F7138}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{B1B7F1AE-C00F-4CC2-82E3-32FC3FFE3560}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{FE6BDE23-52FC-41D4-8B40-F390A9871ADD}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{4D4556AA-6336-4B9A-B471-3B29E101749D}"/>
+    <hyperlink ref="F11" r:id="rId7" xr:uid="{765CC2C4-6FF0-41C6-A669-EC3E697B8171}"/>
+    <hyperlink ref="F12" r:id="rId8" xr:uid="{2C70163B-9506-4752-B67C-59507F376F42}"/>
+    <hyperlink ref="F9" r:id="rId9" xr:uid="{780CE426-8186-4404-B761-C42DCCE19E3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
